--- a/data/availability/projects/palm-hills-developments/97-hills.xlsx
+++ b/data/availability/projects/palm-hills-developments/97-hills.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -859,7 +859,6 @@
       <c r="G2" t="n">
         <v>225.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -916,7 +915,6 @@
       <c r="G3" t="n">
         <v>225.5</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -973,7 +971,6 @@
       <c r="G4" t="n">
         <v>206</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1030,7 +1027,6 @@
       <c r="G5" t="n">
         <v>206</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1063,7 +1059,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1087,7 +1083,6 @@
       <c r="G6" t="n">
         <v>193</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1144,7 +1139,6 @@
       <c r="G7" t="n">
         <v>193</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1177,7 +1171,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1201,7 +1195,6 @@
       <c r="G8" t="n">
         <v>193</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1234,7 +1227,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1258,7 +1251,6 @@
       <c r="G9" t="n">
         <v>193</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1291,7 +1283,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1315,7 +1307,6 @@
       <c r="G10" t="n">
         <v>193</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1348,7 +1339,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1372,7 +1363,6 @@
       <c r="G11" t="n">
         <v>193</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1405,7 +1395,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1429,7 +1419,6 @@
       <c r="G12" t="n">
         <v>193</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1462,7 +1451,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1486,7 +1475,6 @@
       <c r="G13" t="n">
         <v>193</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1519,7 +1507,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1543,7 +1531,6 @@
       <c r="G14" t="n">
         <v>183</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1576,7 +1563,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1600,7 +1587,6 @@
       <c r="G15" t="n">
         <v>183</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1633,7 +1619,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1657,7 +1643,6 @@
       <c r="G16" t="n">
         <v>183</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1690,7 +1675,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1714,7 +1699,6 @@
       <c r="G17" t="n">
         <v>183</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1747,7 +1731,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1771,7 +1755,6 @@
       <c r="G18" t="n">
         <v>183</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1804,7 +1787,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1828,7 +1811,6 @@
       <c r="G19" t="n">
         <v>183</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1861,7 +1843,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1885,7 +1867,6 @@
       <c r="G20" t="n">
         <v>183</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1918,7 +1899,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1942,7 +1923,6 @@
       <c r="G21" t="n">
         <v>183</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1975,7 +1955,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1999,7 +1979,6 @@
       <c r="G22" t="n">
         <v>183</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2032,7 +2011,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2056,7 +2035,6 @@
       <c r="G23" t="n">
         <v>183</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2089,7 +2067,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2113,7 +2091,6 @@
       <c r="G24" t="n">
         <v>183</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2146,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2170,7 +2147,6 @@
       <c r="G25" t="n">
         <v>183</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2203,7 +2179,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2227,7 +2203,6 @@
       <c r="G26" t="n">
         <v>183</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2260,7 +2235,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2284,7 +2259,6 @@
       <c r="G27" t="n">
         <v>183</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2341,7 +2315,6 @@
       <c r="G28" t="n">
         <v>206</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2398,7 +2371,6 @@
       <c r="G29" t="n">
         <v>206</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2455,7 +2427,6 @@
       <c r="G30" t="n">
         <v>251.5</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2512,7 +2483,6 @@
       <c r="G31" t="n">
         <v>251.5</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2569,7 +2539,6 @@
       <c r="G32" t="n">
         <v>251.5</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2626,7 +2595,6 @@
       <c r="G33" t="n">
         <v>251.5</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2683,7 +2651,6 @@
       <c r="G34" t="n">
         <v>416.5</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2740,7 +2707,6 @@
       <c r="G35" t="n">
         <v>416.5</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2773,7 +2739,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2797,7 +2763,6 @@
       <c r="G36" t="n">
         <v>183</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2830,7 +2795,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2854,7 +2819,6 @@
       <c r="G37" t="n">
         <v>183</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2887,7 +2851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2911,7 +2875,6 @@
       <c r="G38" t="n">
         <v>183</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2944,7 +2907,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2968,7 +2931,6 @@
       <c r="G39" t="n">
         <v>183</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3001,7 +2963,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3025,7 +2987,6 @@
       <c r="G40" t="n">
         <v>183</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3058,7 +3019,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3082,7 +3043,6 @@
       <c r="G41" t="n">
         <v>183</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3115,7 +3075,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3139,7 +3099,6 @@
       <c r="G42" t="n">
         <v>183</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3172,7 +3131,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3196,7 +3155,6 @@
       <c r="G43" t="n">
         <v>183</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3229,7 +3187,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Luxury One-Story Mansion</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3253,7 +3211,6 @@
       <c r="G44" t="n">
         <v>183</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3310,7 +3267,6 @@
       <c r="G45" t="n">
         <v>225.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3367,7 +3323,6 @@
       <c r="G46" t="n">
         <v>224</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3424,7 +3379,6 @@
       <c r="G47" t="n">
         <v>224</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3481,7 +3435,6 @@
       <c r="G48" t="n">
         <v>224</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3538,7 +3491,6 @@
       <c r="G49" t="n">
         <v>224</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3595,7 +3547,6 @@
       <c r="G50" t="n">
         <v>206</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3652,7 +3603,6 @@
       <c r="G51" t="n">
         <v>206</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3709,7 +3659,6 @@
       <c r="G52" t="n">
         <v>206</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3766,7 +3715,6 @@
       <c r="G53" t="n">
         <v>206</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3823,7 +3771,6 @@
       <c r="G54" t="n">
         <v>206</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3880,7 +3827,6 @@
       <c r="G55" t="n">
         <v>225.5</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3937,7 +3883,6 @@
       <c r="G56" t="n">
         <v>225.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3994,7 +3939,6 @@
       <c r="G57" t="n">
         <v>225.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/97-hills.xlsx
+++ b/data/availability/projects/palm-hills-developments/97-hills.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Luxury One-Story Mansion</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
